--- a/04_Figures/F04_association/modules/acute/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/acute/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.132142857142857</v>
+        <v>-0.332142857142857</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.480662933137168</v>
+        <v>-1.26963651854388</v>
       </c>
       <c r="F2" t="n">
-        <v>0.638744218884067</v>
+        <v>0.226471759070724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.754879531408442</v>
+        <v>0.4945434579341</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.475</v>
+        <v>-0.0142857142857143</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.94620966033193</v>
+        <v>-0.0515131320740328</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0735708620459136</v>
+        <v>0.959699764598948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.616786139416809</v>
+        <v>0.959699764598948</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.325</v>
+        <v>-0.528571428571428</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.23906820110441</v>
+        <v>-2.24504236852602</v>
       </c>
       <c r="F4" t="n">
-        <v>0.237225438237234</v>
+        <v>0.0427972893094504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.616786139416809</v>
+        <v>0.470770182403954</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0142857142857143</v>
+        <v>0.364285714285714</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0515131320740328</v>
+        <v>1.41036059462917</v>
       </c>
       <c r="F5" t="n">
-        <v>0.959699764598948</v>
+        <v>0.181910259045814</v>
       </c>
       <c r="G5" t="n">
-        <v>0.959699764598948</v>
+        <v>0.4945434579341</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.160714285714286</v>
+        <v>-0.178571428571429</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.587095265748098</v>
+        <v>-0.654366100445603</v>
       </c>
       <c r="F6" t="n">
-        <v>0.567196704580345</v>
+        <v>0.524284360046553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.754879531408442</v>
+        <v>0.661554881899552</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.146428571428571</v>
+        <v>-0.110714285714286</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.533708434419441</v>
+        <v>-0.401655299909643</v>
       </c>
       <c r="F7" t="n">
-        <v>0.602549920983054</v>
+        <v>0.694462647207096</v>
       </c>
       <c r="G7" t="n">
-        <v>0.754879531408442</v>
+        <v>0.763908911927806</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.160714285714286</v>
+        <v>0.364285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.587095265748098</v>
+        <v>1.41036059462917</v>
       </c>
       <c r="F8" t="n">
-        <v>0.567196704580345</v>
+        <v>0.181910259045814</v>
       </c>
       <c r="G8" t="n">
-        <v>0.754879531408442</v>
+        <v>0.4945434579341</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.442857142857143</v>
+        <v>-0.171428571428571</v>
       </c>
       <c r="E9" t="n">
-        <v>1.78090346782642</v>
+        <v>-0.627381920373686</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0982940655468714</v>
+        <v>0.541272176099633</v>
       </c>
       <c r="G9" t="n">
-        <v>0.616786139416809</v>
+        <v>0.661554881899552</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.385714285714286</v>
+        <v>-0.296428571428571</v>
       </c>
       <c r="E10" t="n">
-        <v>1.50735430417727</v>
+        <v>-1.1190856914849</v>
       </c>
       <c r="F10" t="n">
-        <v>0.15563079458596</v>
+        <v>0.283355428434263</v>
       </c>
       <c r="G10" t="n">
-        <v>0.616786139416809</v>
+        <v>0.4945434579341</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0464285714285714</v>
+        <v>0.375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.16758131253873</v>
+        <v>1.45851730441319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.869491525545095</v>
+        <v>0.168432749846746</v>
       </c>
       <c r="G11" t="n">
-        <v>0.941949152673852</v>
+        <v>0.4945434579341</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.146428571428571</v>
+        <v>-0.278571428571429</v>
       </c>
       <c r="E12" t="n">
-        <v>0.533708434419441</v>
+        <v>-1.0458010674983</v>
       </c>
       <c r="F12" t="n">
-        <v>0.602549920983054</v>
+        <v>0.314709473230791</v>
       </c>
       <c r="G12" t="n">
-        <v>0.754879531408442</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.23906820110441</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.237225438237234</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.616786139416809</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.271428571428571</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.01682258925182</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.327789306841173</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.710210164822541</v>
+        <v>0.4945434579341</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.167857142857143</v>
+        <v>-0.171428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6139283620727</v>
+        <v>-0.627381920373686</v>
       </c>
       <c r="F2" t="n">
-        <v>0.549855554227802</v>
+        <v>0.541272176099633</v>
       </c>
       <c r="G2" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.232142857142857</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.860510661125327</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.405098740693649</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.899446993472087</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.285714285714286</v>
+        <v>-0.260714285714286</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.07496769977314</v>
+        <v>-0.973692917115073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.301936351322549</v>
+        <v>0.347979459862794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0357142857142857</v>
+        <v>0.175</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.128851890580845</v>
+        <v>0.640860961835639</v>
       </c>
       <c r="F5" t="n">
-        <v>0.899446993472087</v>
+        <v>0.532748148137859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.153571428571429</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.547021696619878</v>
+        <v>-0.560356865859059</v>
       </c>
       <c r="F6" t="n">
-        <v>0.593630202742588</v>
+        <v>0.584764094941016</v>
       </c>
       <c r="G6" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0678571428571429</v>
+        <v>-0.157142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.245227646009749</v>
+        <v>-0.573714526046661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.810108818710513</v>
+        <v>0.575952600603795</v>
       </c>
       <c r="G7" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0464285714285714</v>
+        <v>0.271428571428571</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.16758131253873</v>
+        <v>1.01682258925182</v>
       </c>
       <c r="F8" t="n">
-        <v>0.869491525545095</v>
+        <v>0.327789306841173</v>
       </c>
       <c r="G8" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.275</v>
+        <v>0.0321428571428571</v>
       </c>
       <c r="E9" t="n">
-        <v>1.03128873603157</v>
+        <v>0.115952634048852</v>
       </c>
       <c r="F9" t="n">
-        <v>0.321211173319377</v>
+        <v>0.909462117094591</v>
       </c>
       <c r="G9" t="n">
-        <v>0.899446993472087</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.192857142857143</v>
+        <v>-0.107142857142857</v>
       </c>
       <c r="E10" t="n">
-        <v>0.708660102968926</v>
+        <v>-0.38854567548164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.491048701605223</v>
+        <v>0.703901001626162</v>
       </c>
       <c r="G10" t="n">
-        <v>0.899446993472087</v>
+        <v>0.860323446431975</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.217857142857143</v>
+        <v>0.182142857142857</v>
       </c>
       <c r="E11" t="n">
-        <v>0.804826493639811</v>
+        <v>0.667897955721517</v>
       </c>
       <c r="F11" t="n">
-        <v>0.435392673515538</v>
+        <v>0.515881681707039</v>
       </c>
       <c r="G11" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.214285714285714</v>
+        <v>-0.257142857142857</v>
       </c>
       <c r="E12" t="n">
-        <v>0.790992066456966</v>
+        <v>-0.959403223600247</v>
       </c>
       <c r="F12" t="n">
-        <v>0.443140934823514</v>
+        <v>0.354860363650609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.899446993472087</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.121428571428571</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.441080862981928</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.66640111372339</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.899446993472087</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0428571428571429</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.154665731331055</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8794603130259</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.899446993472087</v>
+        <v>0.804050630543897</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.139285714285714</v>
+        <v>-0.282142857142857</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.507145317953373</v>
+        <v>-1.06036043455401</v>
       </c>
       <c r="F2" t="n">
-        <v>0.620546087627901</v>
+        <v>0.308284456820055</v>
       </c>
       <c r="G2" t="n">
-        <v>0.806709913916272</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.289285714285714</v>
+        <v>0.103571428571429</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.08962373769732</v>
+        <v>0.375451266447069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.295665361004378</v>
+        <v>0.713379630628729</v>
       </c>
       <c r="G3" t="n">
-        <v>0.769525102865797</v>
+        <v>0.79518705780703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.289285714285714</v>
+        <v>-0.303571428571428</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.08962373769732</v>
+        <v>-1.14875354327913</v>
       </c>
       <c r="F4" t="n">
-        <v>0.295665361004378</v>
+        <v>0.271355836003868</v>
       </c>
       <c r="G4" t="n">
-        <v>0.769525102865797</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.075</v>
+        <v>0.221428571428571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.271180115299783</v>
+        <v>0.818694863860519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.790510794155268</v>
+        <v>0.42771371901637</v>
       </c>
       <c r="G5" t="n">
-        <v>0.856386693668207</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.207142857142857</v>
+        <v>-0.210714285714286</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.763422283414352</v>
+        <v>-0.777190891009981</v>
       </c>
       <c r="F6" t="n">
-        <v>0.45884280496347</v>
+        <v>0.450957865215285</v>
       </c>
       <c r="G6" t="n">
-        <v>0.769525102865797</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.075</v>
+        <v>-0.125</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.271180115299783</v>
+        <v>-0.454256762579498</v>
       </c>
       <c r="F7" t="n">
-        <v>0.790510794155268</v>
+        <v>0.65713566818695</v>
       </c>
       <c r="G7" t="n">
-        <v>0.856386693668207</v>
+        <v>0.79518705780703</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.175</v>
+        <v>0.257142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.640860961835639</v>
+        <v>0.959403223600247</v>
       </c>
       <c r="F8" t="n">
-        <v>0.532748148137859</v>
+        <v>0.354860363650609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.769525102865797</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.257142857142857</v>
+        <v>0.00357142857142857</v>
       </c>
       <c r="E9" t="n">
-        <v>0.959403223600247</v>
+        <v>0.0128770509652542</v>
       </c>
       <c r="F9" t="n">
-        <v>0.354860363650609</v>
+        <v>0.989921406880978</v>
       </c>
       <c r="G9" t="n">
-        <v>0.769525102865797</v>
+        <v>0.989921406880978</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.246428571428571</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.916783578893438</v>
+        <v>-0.362371537669739</v>
       </c>
       <c r="F10" t="n">
-        <v>0.375950515973805</v>
+        <v>0.722897325279118</v>
       </c>
       <c r="G10" t="n">
-        <v>0.769525102865797</v>
+        <v>0.79518705780703</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.235714285714286</v>
+        <v>0.267857142857143</v>
       </c>
       <c r="E11" t="n">
-        <v>0.874521871729162</v>
+        <v>1.0024017876421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.397702945903273</v>
+        <v>0.334443600512354</v>
       </c>
       <c r="G11" t="n">
-        <v>0.769525102865797</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.253571428571429</v>
+        <v>-0.275</v>
       </c>
       <c r="E12" t="n">
-        <v>0.945155625533198</v>
+        <v>-1.03128873603157</v>
       </c>
       <c r="F12" t="n">
-        <v>0.36181610381589</v>
+        <v>0.321211173319377</v>
       </c>
       <c r="G12" t="n">
-        <v>0.769525102865797</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.178571428571429</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.654366100445603</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.524284360046553</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.769525102865797</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0357142857142857</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.128851890580845</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.899446993472087</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.899446993472087</v>
+        <v>0.708648073909734</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.175</v>
+        <v>-0.275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.640860961835639</v>
+        <v>-1.03128873603157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.532748148137859</v>
+        <v>0.321211173319377</v>
       </c>
       <c r="G2" t="n">
-        <v>0.769525102865797</v>
+        <v>0.588887151085524</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.492857142857143</v>
+        <v>-0.075</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.04229488421644</v>
+        <v>-0.271180115299783</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0619510067141686</v>
+        <v>0.790510794155268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.30970294274896</v>
+        <v>0.934570930455368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-0.496428571428571</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.180503334135647</v>
+        <v>-2.06191096706449</v>
       </c>
       <c r="F4" t="n">
-        <v>0.859540943467457</v>
+        <v>0.059797413749924</v>
       </c>
       <c r="G4" t="n">
-        <v>0.909462117094591</v>
+        <v>0.574713463742366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0321428571428571</v>
+        <v>0.435714285714286</v>
       </c>
       <c r="E5" t="n">
-        <v>0.115952634048852</v>
+        <v>1.74537976551</v>
       </c>
       <c r="F5" t="n">
-        <v>0.909462117094591</v>
+        <v>0.104493357044066</v>
       </c>
       <c r="G5" t="n">
-        <v>0.909462117094591</v>
+        <v>0.574713463742366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0821428571428571</v>
+        <v>0.0535714285714286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.297174565403596</v>
+        <v>0.193432297524523</v>
       </c>
       <c r="F6" t="n">
-        <v>0.771028565288177</v>
+        <v>0.849609936777607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.909462117094591</v>
+        <v>0.934570930455368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.175</v>
+        <v>0.207142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.640860961835639</v>
+        <v>0.763422283414352</v>
       </c>
       <c r="F7" t="n">
-        <v>0.532748148137859</v>
+        <v>0.45884280496347</v>
       </c>
       <c r="G7" t="n">
-        <v>0.769525102865797</v>
+        <v>0.630908856824771</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0357142857142857</v>
+        <v>0.232142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.128851890580845</v>
+        <v>0.860510661125327</v>
       </c>
       <c r="F8" t="n">
-        <v>0.899446993472087</v>
+        <v>0.405098740693649</v>
       </c>
       <c r="G8" t="n">
-        <v>0.909462117094591</v>
+        <v>0.630908856824771</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.446428571428571</v>
+        <v>-0.325</v>
       </c>
       <c r="E9" t="n">
-        <v>1.79882257167426</v>
+        <v>-1.23906820110441</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0952932131535262</v>
+        <v>0.237225438237234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.30970294274896</v>
+        <v>0.588887151085524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.475</v>
+        <v>-0.321428571428571</v>
       </c>
       <c r="E10" t="n">
-        <v>1.94620966033193</v>
+        <v>-1.22387347685125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0735708620459136</v>
+        <v>0.242719046801668</v>
       </c>
       <c r="G10" t="n">
-        <v>0.30970294274896</v>
+        <v>0.588887151085524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.528571428571428</v>
+        <v>0.275</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.24504236852602</v>
+        <v>1.03128873603157</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0427972893094504</v>
+        <v>0.321211173319377</v>
       </c>
       <c r="G11" t="n">
-        <v>0.30970294274896</v>
+        <v>0.588887151085524</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.207142857142857</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.763422283414352</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.45884280496347</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.769525102865797</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.253571428571429</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.945155625533198</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.36181610381589</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.769525102865797</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.407142857142857</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.60721646388664</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.132012663779854</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.34323292582762</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0681621203167466</v>
+        <v>-0.342604341592069</v>
       </c>
       <c r="E2" t="n">
-        <v>0.246334931307856</v>
+        <v>-1.31485268915867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.809269818463732</v>
+        <v>0.211282611836316</v>
       </c>
       <c r="G2" t="n">
-        <v>0.956409785457138</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.251123601166961</v>
+        <v>0.238567421108613</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.935414346693485</v>
+        <v>0.88574204092103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.366626533995358</v>
+        <v>0.391846434815954</v>
       </c>
       <c r="G3" t="n">
-        <v>0.636750456575926</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.202692620941904</v>
+        <v>-0.118386840550139</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.746310238430464</v>
+        <v>-0.429872883365625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.468762097822115</v>
+        <v>0.674327856137202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.677100807965278</v>
+        <v>0.876229265560489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.24394864113362</v>
+        <v>-0.10224318047512</v>
       </c>
       <c r="E5" t="n">
-        <v>0.90697059149668</v>
+        <v>-0.370585105377105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.380926875394842</v>
+        <v>0.7169148536404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.636750456575926</v>
+        <v>0.876229265560489</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.238567421108613</v>
+        <v>-0.270854741258651</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.88574204092103</v>
+        <v>-1.01450252795154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.391846434815954</v>
+        <v>0.328853340588878</v>
       </c>
       <c r="G6" t="n">
-        <v>0.636750456575926</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.166817820775196</v>
+        <v>0.057399680266734</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.610017939143456</v>
+        <v>0.207299269010996</v>
       </c>
       <c r="F7" t="n">
-        <v>0.55236442356416</v>
+        <v>0.838988074179233</v>
       </c>
       <c r="G7" t="n">
-        <v>0.718073750633408</v>
+        <v>0.922886881597157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.256504821191968</v>
+        <v>-0.252917341175297</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.956854823646126</v>
+        <v>-0.942550755296172</v>
       </c>
       <c r="F8" t="n">
-        <v>0.356097527461551</v>
+        <v>0.363098086913973</v>
       </c>
       <c r="G8" t="n">
-        <v>0.636750456575926</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.254711081183632</v>
+        <v>0.0107624400500126</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.949697547906574</v>
+        <v>0.0388067770112516</v>
       </c>
       <c r="F9" t="n">
-        <v>0.359588401239409</v>
+        <v>0.969634067313828</v>
       </c>
       <c r="G9" t="n">
-        <v>0.636750456575926</v>
+        <v>0.969634067313828</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0376685401750442</v>
+        <v>0.3695104417171</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.135912311576948</v>
+        <v>1.43376101783834</v>
       </c>
       <c r="F10" t="n">
-        <v>0.893972668301745</v>
+        <v>0.175253114967885</v>
       </c>
       <c r="G10" t="n">
-        <v>0.964575794778578</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.335429381558727</v>
+        <v>0.182961480850215</v>
       </c>
       <c r="E11" t="n">
-        <v>1.28378337044591</v>
+        <v>0.671003484125131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.221628311967696</v>
+        <v>0.513964363158746</v>
       </c>
       <c r="G11" t="n">
-        <v>0.636750456575926</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.24753612115029</v>
+        <v>-0.206280100958575</v>
       </c>
       <c r="E12" t="n">
-        <v>0.92117228812172</v>
+        <v>-0.760100985079688</v>
       </c>
       <c r="F12" t="n">
-        <v>0.373739503102516</v>
+        <v>0.460757706578496</v>
       </c>
       <c r="G12" t="n">
-        <v>0.636750456575926</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0125561800583481</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0452755201812447</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.964575794778578</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.964575794778578</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.403591501875474</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.59045509839346</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.135746689365551</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.636750456575926</v>
+        <v>0.807658284963743</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.154185396052667</v>
+        <v>0.222467500018848</v>
       </c>
       <c r="E2" t="n">
-        <v>0.540578148593222</v>
+        <v>0.790458840417768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.598689043816195</v>
+        <v>0.444601039194887</v>
       </c>
       <c r="G2" t="n">
-        <v>0.778295756961054</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0308370792105334</v>
+        <v>-0.414097920827163</v>
       </c>
       <c r="E3" t="n">
-        <v>0.106873602399721</v>
+        <v>-1.57594628759105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.916655212625141</v>
+        <v>0.141021429013163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.993043147010569</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.332599925770753</v>
+        <v>0.0748900495112955</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2217145701591</v>
+        <v>0.260157315962355</v>
       </c>
       <c r="F4" t="n">
-        <v>0.245273343251503</v>
+        <v>0.79915261522139</v>
       </c>
       <c r="G4" t="n">
-        <v>0.670711635961733</v>
+        <v>0.976742085270587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.359031707951211</v>
+        <v>0.202643663383505</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3325710080165</v>
+        <v>0.716851077535768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.207423814064759</v>
+        <v>0.487184653179536</v>
       </c>
       <c r="G5" t="n">
-        <v>0.670711635961733</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2254,12 +2018,12 @@
         <v>0.36115241936401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.670711635961733</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.299560198045182</v>
+        <v>0.154185396052667</v>
       </c>
       <c r="E7" t="n">
-        <v>1.08765490558959</v>
+        <v>0.540578148593222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.298110932619832</v>
+        <v>0.598689043816195</v>
       </c>
       <c r="G7" t="n">
-        <v>0.670711635961733</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0418503217857239</v>
+        <v>0.180617178233124</v>
       </c>
       <c r="E8" t="n">
-        <v>0.145100891416265</v>
+        <v>0.636138528098248</v>
       </c>
       <c r="F8" t="n">
-        <v>0.887039880140612</v>
+        <v>0.536630844482229</v>
       </c>
       <c r="G8" t="n">
-        <v>0.993043147010569</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.290749603985029</v>
+        <v>-0.0044052970300762</v>
       </c>
       <c r="E9" t="n">
-        <v>1.05266203766172</v>
+        <v>-0.0152605446357296</v>
       </c>
       <c r="F9" t="n">
-        <v>0.313231629565861</v>
+        <v>0.988075108981028</v>
       </c>
       <c r="G9" t="n">
-        <v>0.670711635961733</v>
+        <v>0.988075108981028</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.167401287142896</v>
+        <v>-0.202643663383505</v>
       </c>
       <c r="E10" t="n">
-        <v>0.588195184263463</v>
+        <v>-0.716851077535768</v>
       </c>
       <c r="F10" t="n">
-        <v>0.567306849204212</v>
+        <v>0.487184653179536</v>
       </c>
       <c r="G10" t="n">
-        <v>0.778295756961054</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.229075445563963</v>
+        <v>-0.0154185396052667</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.815218360831655</v>
+        <v>-0.0534177378629159</v>
       </c>
       <c r="F11" t="n">
-        <v>0.430830581603804</v>
+        <v>0.958278064313914</v>
       </c>
       <c r="G11" t="n">
-        <v>0.700099695106182</v>
+        <v>0.988075108981028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.411895272312125</v>
+        <v>0.343613168345944</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.56584529935911</v>
+        <v>1.26748657015974</v>
       </c>
       <c r="F12" t="n">
-        <v>0.143362140186007</v>
+        <v>0.229025220716849</v>
       </c>
       <c r="G12" t="n">
-        <v>0.670711635961733</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.314978737650449</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.14963630446523</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.272690913956299</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.670711635961733</v>
+        <v>0.823197435247269</v>
       </c>
     </row>
   </sheetData>
@@ -2454,71 +2172,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.160714285714286</v>
+        <v>0.296428571428571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.264317821804572</v>
+        <v>0.202643663383505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24394864113362</v>
+        <v>0.206280100958575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.167857142857143</v>
+        <v>0.171428571428571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,33 +2323,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.207142857142857</v>
+        <v>0.221428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.207142857142857</v>
+        <v>0.275</v>
       </c>
     </row>
   </sheetData>
